--- a/Accounts.xlsx
+++ b/Accounts.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Indalwai Account" sheetId="2" r:id="rId1"/>
@@ -162,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="138">
   <si>
     <t>Indalwai Account</t>
   </si>
@@ -573,6 +573,9 @@
   </si>
   <si>
     <t>Culvert Drawing for Ramagundam Site</t>
+  </si>
+  <si>
+    <t>Peddapally Building M.Book Measurements</t>
   </si>
 </sst>
 </file>
@@ -7333,14 +7336,28 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75">
-      <c r="A21" s="68"/>
-      <c r="B21" s="74"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="69"/>
-      <c r="E21" s="70"/>
+    <row r="21" spans="1:7" ht="47.25">
+      <c r="A21" s="68">
+        <v>18</v>
+      </c>
+      <c r="B21" s="74" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" s="69">
+        <v>44763</v>
+      </c>
+      <c r="D21" s="69">
+        <v>44764</v>
+      </c>
+      <c r="E21" s="70">
+        <f t="shared" ref="E21" si="6">+D21-C21+1</f>
+        <v>2</v>
+      </c>
       <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
+      <c r="G21" s="68">
+        <f t="shared" ref="G21" si="7">+E21*1500</f>
+        <v>3000</v>
+      </c>
     </row>
     <row r="22" spans="1:7" ht="15.75">
       <c r="A22" s="68"/>
@@ -7374,7 +7391,7 @@
       </c>
       <c r="G24" s="73">
         <f>SUM(G4:G23)</f>
-        <v>153393</v>
+        <v>156393</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -7393,7 +7410,7 @@
       </c>
       <c r="G27">
         <f>+G24</f>
-        <v>153393</v>
+        <v>156393</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.75">
@@ -7402,7 +7419,7 @@
       </c>
       <c r="G28" s="79">
         <f>+G27-F27</f>
-        <v>-10107</v>
+        <v>-7107</v>
       </c>
     </row>
   </sheetData>

--- a/Accounts.xlsx
+++ b/Accounts.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Indalwai Account" sheetId="2" r:id="rId1"/>
@@ -162,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="140">
   <si>
     <t>Indalwai Account</t>
   </si>
@@ -576,6 +576,12 @@
   </si>
   <si>
     <t>Peddapally Building M.Book Measurements</t>
+  </si>
+  <si>
+    <t>Added in daiy basis</t>
+  </si>
+  <si>
+    <t>Peddapally building measurements at Ramagundam Site</t>
   </si>
 </sst>
 </file>
@@ -777,7 +783,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1035,6 +1041,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2262,7 +2280,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:G224"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="6" customWidth="1"/>
@@ -4350,7 +4368,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="193" spans="1:4">
+    <row r="193" spans="1:5">
       <c r="A193" s="14"/>
       <c r="B193" s="13" t="s">
         <v>123</v>
@@ -4360,7 +4378,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="194" spans="1:4">
+    <row r="194" spans="1:5">
       <c r="A194" s="14"/>
       <c r="B194" s="13" t="s">
         <v>122</v>
@@ -4371,7 +4389,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="195" spans="1:4">
+    <row r="195" spans="1:5">
       <c r="A195" s="14">
         <v>44636</v>
       </c>
@@ -4383,7 +4401,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="196" spans="1:4">
+    <row r="196" spans="1:5">
       <c r="A196" s="14"/>
       <c r="B196" s="13" t="s">
         <v>3</v>
@@ -4393,7 +4411,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="15.75">
+    <row r="197" spans="1:5" ht="15.75">
       <c r="A197" s="40">
         <v>44637</v>
       </c>
@@ -4405,7 +4423,7 @@
       </c>
       <c r="D197" s="55"/>
     </row>
-    <row r="198" spans="1:4">
+    <row r="198" spans="1:5">
       <c r="A198" s="14">
         <v>44637</v>
       </c>
@@ -4418,7 +4436,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="199" spans="1:4">
+    <row r="199" spans="1:5">
       <c r="A199" s="14"/>
       <c r="B199" s="13" t="s">
         <v>125</v>
@@ -4428,7 +4446,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="200" spans="1:4">
+    <row r="200" spans="1:5">
       <c r="A200" s="14"/>
       <c r="B200" s="13" t="s">
         <v>3</v>
@@ -4438,7 +4456,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="201" spans="1:4">
+    <row r="201" spans="1:5">
       <c r="A201" s="14">
         <v>44642</v>
       </c>
@@ -4450,7 +4468,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="202" spans="1:4">
+    <row r="202" spans="1:5">
       <c r="A202" s="14"/>
       <c r="B202" s="13" t="s">
         <v>116</v>
@@ -4461,7 +4479,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="203" spans="1:4">
+    <row r="203" spans="1:5">
       <c r="A203" s="14">
         <v>44664</v>
       </c>
@@ -4474,7 +4492,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="204" spans="1:4">
+    <row r="204" spans="1:5">
       <c r="A204" s="14"/>
       <c r="B204" s="13" t="s">
         <v>3</v>
@@ -4484,7 +4502,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="205" spans="1:4">
+    <row r="205" spans="1:5">
       <c r="A205" s="14"/>
       <c r="B205" s="13" t="s">
         <v>23</v>
@@ -4494,7 +4512,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="206" spans="1:4" ht="18.75">
+    <row r="206" spans="1:5" ht="18.75">
       <c r="A206" s="14"/>
       <c r="B206" s="43" t="s">
         <v>30</v>
@@ -4508,10 +4526,13 @@
         <v>26393</v>
       </c>
     </row>
-    <row r="207" spans="1:4">
-      <c r="D207" s="6">
+    <row r="207" spans="1:5">
+      <c r="D207" s="92">
         <f>+C206-D206</f>
         <v>-3393</v>
+      </c>
+      <c r="E207" s="93" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4542,105 +4563,190 @@
         <v>19</v>
       </c>
     </row>
-    <row r="213" spans="1:4" ht="15.75">
-      <c r="A213" s="34">
+    <row r="213" spans="1:4">
+      <c r="A213" s="49">
+        <v>44694</v>
+      </c>
+      <c r="B213" s="65" t="s">
+        <v>3</v>
+      </c>
+      <c r="C213" s="5"/>
+      <c r="D213" s="5">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="15.75">
+      <c r="A214" s="34"/>
+      <c r="B214" s="65" t="s">
+        <v>85</v>
+      </c>
+      <c r="C214" s="5"/>
+      <c r="D214" s="5">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" ht="15.75">
+      <c r="A215" s="34">
         <v>44696</v>
       </c>
-      <c r="B213" s="35" t="s">
+      <c r="B215" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="C213" s="2">
+      <c r="C215" s="2">
         <v>2000</v>
       </c>
-      <c r="D213" s="5"/>
-    </row>
-    <row r="214" spans="1:4">
-      <c r="A214" s="49"/>
-      <c r="B214" s="48" t="s">
+      <c r="D215" s="5"/>
+    </row>
+    <row r="216" spans="1:4">
+      <c r="A216" s="49"/>
+      <c r="B216" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="C214" s="47"/>
-      <c r="D214" s="47">
+      <c r="C216" s="47"/>
+      <c r="D216" s="47">
         <f>90+250+350</f>
         <v>690</v>
       </c>
     </row>
-    <row r="215" spans="1:4">
-      <c r="A215" s="49"/>
-      <c r="B215" s="48" t="s">
+    <row r="217" spans="1:4">
+      <c r="A217" s="49"/>
+      <c r="B217" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="C215" s="47"/>
-      <c r="D215" s="47">
+      <c r="C217" s="47"/>
+      <c r="D217" s="47">
         <v>130</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="15.75">
-      <c r="A216" s="49">
+    <row r="218" spans="1:4" ht="15.75">
+      <c r="A218" s="49">
         <v>44701</v>
       </c>
-      <c r="B216" s="48" t="s">
+      <c r="B218" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="C216" s="2"/>
-      <c r="D216" s="47">
+      <c r="C218" s="2"/>
+      <c r="D218" s="47">
         <v>590</v>
       </c>
     </row>
-    <row r="217" spans="1:4" ht="15.75">
-      <c r="A217" s="49"/>
-      <c r="B217" s="48"/>
-      <c r="C217" s="2"/>
-      <c r="D217" s="47"/>
-    </row>
-    <row r="218" spans="1:4" ht="15.75">
-      <c r="A218" s="49"/>
-      <c r="B218" s="48"/>
-      <c r="C218" s="2"/>
-      <c r="D218" s="47"/>
-    </row>
-    <row r="219" spans="1:4" ht="15.75">
-      <c r="A219" s="49"/>
-      <c r="B219" s="48"/>
-      <c r="C219" s="2"/>
-      <c r="D219" s="47"/>
-    </row>
-    <row r="220" spans="1:4" ht="15.75">
-      <c r="A220" s="49"/>
-      <c r="B220" s="48"/>
-      <c r="C220" s="2"/>
-      <c r="D220" s="47"/>
+    <row r="219" spans="1:4">
+      <c r="A219" s="63">
+        <v>44706</v>
+      </c>
+      <c r="B219" s="65" t="s">
+        <v>3</v>
+      </c>
+      <c r="C219" s="5"/>
+      <c r="D219" s="5">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4">
+      <c r="A220" s="63"/>
+      <c r="B220" s="65" t="s">
+        <v>85</v>
+      </c>
+      <c r="C220" s="5"/>
+      <c r="D220" s="5">
+        <v>60</v>
+      </c>
     </row>
     <row r="221" spans="1:4" ht="15.75">
-      <c r="A221" s="49"/>
-      <c r="B221" s="48"/>
+      <c r="A221" s="49">
+        <v>44708</v>
+      </c>
+      <c r="B221" s="48" t="s">
+        <v>3</v>
+      </c>
       <c r="C221" s="2"/>
-      <c r="D221" s="47"/>
+      <c r="D221" s="47">
+        <v>120</v>
+      </c>
     </row>
     <row r="222" spans="1:4" ht="15.75">
-      <c r="A222" s="49"/>
-      <c r="B222" s="48"/>
-      <c r="C222" s="2"/>
-      <c r="D222" s="47"/>
-    </row>
-    <row r="223" spans="1:4" ht="18.75">
+      <c r="A222" s="34">
+        <v>44771</v>
+      </c>
+      <c r="B222" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C222" s="2">
+        <v>2000</v>
+      </c>
+      <c r="D222" s="5"/>
+    </row>
+    <row r="223" spans="1:4" ht="15.75">
       <c r="A223" s="34"/>
-      <c r="B223" s="77" t="s">
+      <c r="B223" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="C223" s="2"/>
+      <c r="D223" s="5">
+        <f>900+150+100+370</f>
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4">
+      <c r="A224" s="49">
+        <v>44772</v>
+      </c>
+      <c r="B224" s="90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C224" s="49"/>
+      <c r="D224" s="5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4">
+      <c r="A225" s="49"/>
+      <c r="B225" s="90"/>
+      <c r="C225" s="49"/>
+      <c r="D225" s="5"/>
+    </row>
+    <row r="226" spans="1:4">
+      <c r="A226" s="49"/>
+      <c r="B226" s="90"/>
+      <c r="C226" s="49"/>
+      <c r="D226" s="5"/>
+    </row>
+    <row r="227" spans="1:4">
+      <c r="A227" s="91"/>
+      <c r="B227" s="90"/>
+      <c r="C227" s="49"/>
+      <c r="D227" s="5"/>
+    </row>
+    <row r="228" spans="1:4">
+      <c r="A228" s="49"/>
+      <c r="B228" s="90"/>
+      <c r="C228" s="49"/>
+      <c r="D228" s="5"/>
+    </row>
+    <row r="229" spans="1:4">
+      <c r="A229" s="49"/>
+      <c r="B229" s="90"/>
+      <c r="C229" s="49"/>
+      <c r="D229" s="5"/>
+    </row>
+    <row r="230" spans="1:4" ht="18.75">
+      <c r="A230" s="34"/>
+      <c r="B230" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="C223" s="78">
-        <f>SUM(C213:C222)</f>
-        <v>2000</v>
-      </c>
-      <c r="D223" s="78">
-        <f>SUM(D213:D222)</f>
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4">
-      <c r="D224" s="6">
-        <f>+C223-D223</f>
-        <v>590</v>
+      <c r="C230" s="78">
+        <f>SUM(C213:C229)</f>
+        <v>4000</v>
+      </c>
+      <c r="D230" s="78">
+        <f>SUM(D213:D229)</f>
+        <v>3550</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4">
+      <c r="D231" s="6">
+        <f>+C230-D230</f>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -4661,7 +4767,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:N168"/>
+  <dimension ref="A1:N163"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="6" customWidth="1"/>
@@ -6768,109 +6874,57 @@
       <c r="D156" s="5"/>
     </row>
     <row r="157" spans="1:4">
-      <c r="A157" s="63"/>
-      <c r="B157" s="65" t="s">
-        <v>3</v>
-      </c>
-      <c r="C157" s="5"/>
-      <c r="D157" s="5">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4">
+      <c r="A157" s="62">
+        <v>44708</v>
+      </c>
+      <c r="B157" s="75" t="s">
+        <v>20</v>
+      </c>
+      <c r="C157" s="64">
+        <v>1000</v>
+      </c>
+      <c r="D157" s="5"/>
+    </row>
+    <row r="158" spans="1:4" ht="15.75">
       <c r="A158" s="63"/>
-      <c r="B158" s="65" t="s">
-        <v>85</v>
-      </c>
-      <c r="C158" s="5"/>
-      <c r="D158" s="5">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4">
-      <c r="A159" s="63">
-        <v>44706</v>
-      </c>
-      <c r="B159" s="65" t="s">
-        <v>3</v>
-      </c>
-      <c r="C159" s="5"/>
-      <c r="D159" s="5">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4">
-      <c r="A160" s="63"/>
-      <c r="B160" s="65" t="s">
-        <v>85</v>
-      </c>
-      <c r="C160" s="5"/>
-      <c r="D160" s="5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4">
-      <c r="A161" s="62">
-        <v>44708</v>
-      </c>
-      <c r="B161" s="75" t="s">
-        <v>20</v>
-      </c>
-      <c r="C161" s="64">
-        <v>1000</v>
-      </c>
-      <c r="D161" s="5"/>
-    </row>
-    <row r="162" spans="1:4" ht="15.75">
-      <c r="A162" s="63"/>
-      <c r="B162" s="48" t="s">
+      <c r="B158" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="C162" s="2"/>
-      <c r="D162" s="47">
+      <c r="C158" s="2"/>
+      <c r="D158" s="47">
         <f>100+90+270+250+800</f>
         <v>1510</v>
       </c>
     </row>
-    <row r="163" spans="1:4" ht="15.75">
-      <c r="A163" s="63"/>
-      <c r="B163" s="48" t="s">
-        <v>3</v>
-      </c>
-      <c r="C163" s="2"/>
-      <c r="D163" s="47">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4">
-      <c r="A164" s="5"/>
-      <c r="B164" s="65"/>
-      <c r="C164" s="5"/>
-      <c r="D164" s="5"/>
-    </row>
-    <row r="165" spans="1:4">
-      <c r="A165" s="5"/>
-      <c r="B165" s="65"/>
-      <c r="C165" s="64">
-        <f>SUM(C125:C164)</f>
+    <row r="159" spans="1:4">
+      <c r="A159" s="5"/>
+      <c r="B159" s="65"/>
+      <c r="C159" s="5"/>
+      <c r="D159" s="5"/>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="5"/>
+      <c r="B160" s="65"/>
+      <c r="C160" s="64">
+        <f>SUM(C125:C159)</f>
         <v>5000</v>
       </c>
-      <c r="D165" s="66">
-        <f>SUM(D125:D164)</f>
-        <v>5539</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4">
-      <c r="D166" s="66">
-        <f>+C165-D165</f>
-        <v>-539</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4">
-      <c r="D167" s="60"/>
-    </row>
-    <row r="168" spans="1:4">
-      <c r="D168" s="60"/>
+      <c r="D160" s="66">
+        <f>SUM(D125:D159)</f>
+        <v>4959</v>
+      </c>
+    </row>
+    <row r="161" spans="4:4">
+      <c r="D161" s="66">
+        <f>+C160-D160</f>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="162" spans="4:4">
+      <c r="D162" s="60"/>
+    </row>
+    <row r="163" spans="4:4">
+      <c r="D163" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6892,7 +6946,7 @@
     <tabColor rgb="FFFF0000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
@@ -7350,23 +7404,32 @@
         <v>44764</v>
       </c>
       <c r="E21" s="70">
-        <f t="shared" ref="E21" si="6">+D21-C21+1</f>
+        <f t="shared" ref="E21:E22" si="6">+D21-C21+1</f>
         <v>2</v>
       </c>
       <c r="F21" s="68"/>
       <c r="G21" s="68">
-        <f t="shared" ref="G21" si="7">+E21*1500</f>
+        <f t="shared" ref="G21:G22" si="7">+E21*1500</f>
         <v>3000</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.75">
-      <c r="A22" s="68"/>
-      <c r="B22" s="74"/>
-      <c r="C22" s="69"/>
+    <row r="22" spans="1:7" ht="47.25">
+      <c r="A22" s="68">
+        <v>19</v>
+      </c>
+      <c r="B22" s="74" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="69">
+        <v>44772</v>
+      </c>
       <c r="D22" s="69"/>
       <c r="E22" s="70"/>
       <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
+      <c r="G22" s="68">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:7" ht="15.75">
       <c r="A23" s="68"/>
@@ -7378,47 +7441,92 @@
       <c r="G23" s="68"/>
     </row>
     <row r="24" spans="1:7" ht="15.75">
-      <c r="A24" s="5"/>
-      <c r="B24" s="71"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="72" t="s">
+      <c r="A24" s="68"/>
+      <c r="B24" s="74"/>
+      <c r="C24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+    </row>
+    <row r="25" spans="1:7" ht="15.75">
+      <c r="A25" s="68"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+    </row>
+    <row r="26" spans="1:7" ht="15.75">
+      <c r="A26" s="68"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+    </row>
+    <row r="27" spans="1:7" ht="15.75">
+      <c r="A27" s="68"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="68"/>
+      <c r="G27" s="68"/>
+    </row>
+    <row r="28" spans="1:7" ht="15.75">
+      <c r="A28" s="68"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="69"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="68"/>
+    </row>
+    <row r="29" spans="1:7" ht="15.75">
+      <c r="A29" s="5"/>
+      <c r="B29" s="71"/>
+      <c r="C29" s="63"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="72" t="s">
         <v>30</v>
       </c>
-      <c r="F24" s="73">
-        <f>SUM(F4:F23)</f>
+      <c r="F29" s="73">
+        <f>SUM(F4:F28)</f>
         <v>163500</v>
       </c>
-      <c r="G24" s="73">
-        <f>SUM(G4:G23)</f>
+      <c r="G29" s="73">
+        <f>SUM(G4:G28)</f>
         <v>156393</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="6"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="59"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="60"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="F27">
-        <f>+F24</f>
+    <row r="30" spans="1:7">
+      <c r="A30" s="6"/>
+      <c r="B30" s="58"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="F32">
+        <f>+F29</f>
         <v>163500</v>
       </c>
-      <c r="G27">
-        <f>+G24</f>
+      <c r="G32">
+        <f>+G29</f>
         <v>156393</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75">
-      <c r="E28" t="s">
+    <row r="33" spans="5:7" ht="15.75">
+      <c r="E33" t="s">
         <v>129</v>
       </c>
-      <c r="G28" s="79">
-        <f>+G27-F27</f>
+      <c r="G33" s="79">
+        <f>+G32-F32</f>
         <v>-7107</v>
       </c>
     </row>
